--- a/sampleprojects/TaxReturn/excel/states/NM.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/NM.xlsx
@@ -9,14 +9,15 @@
   <sheets>
     <sheet name="nm tax" sheetId="2" r:id="rId4"/>
     <sheet name="NM Military Retirement Exclusio" sheetId="3" r:id="rId6"/>
-    <sheet name="EDD" sheetId="4" r:id="rId7"/>
+    <sheet name="NM Tax Table" sheetId="4" r:id="rId7"/>
+    <sheet name="EDD" sheetId="5" r:id="rId8"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="247">
   <si>
     <t>DT: nm tax</t>
   </si>
@@ -42,25 +43,43 @@
     <t>DSL: INITIAL ACTIONS</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t>set result.nm_limit_1 = nm_single_bracket_1_limit; set result.nm_limit_2 = nm_single_bracket_2_limit; set result.nm_limit_3 = nm_single_bracket_3_limit; set result.nm_limit_4 = nm_single_bracket_4_limit; set result.nm_high_base = nm_single_high_base; set result.nm_top_threshold = nm_single_bracket_5_limit; set result.nm_top_base = nm_single_top_base; set result.nm_lmi_limit = nm_lmi_limit_single; set result.nm_lmi_base = nm_lmi_base_single; set result.nm_lmi_rate = nm_lmi_rate_single; set result.nm_dependent_deduction = 0.0</t>
+  </si>
+  <si>
     <t>CONDITIONS: COMMENTS</t>
   </si>
   <si>
     <t>DSL: CONDITIONS</t>
   </si>
   <si>
-    <t>Head of household</t>
-  </si>
-  <si>
-    <t>job.filing_status is equal to "HOH"</t>
-  </si>
-  <si>
-    <t>N</t>
+    <t>MFJ or Head of Household: joint brackets and the line 13 dependent deduction</t>
+  </si>
+  <si>
+    <t>job.filing_status is equal to "MFJ" or job.filing_status is equal to "HOH"</t>
   </si>
   <si>
     <t>Y</t>
   </si>
   <si>
-    <t/>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Surviving Spouse: joint brackets, no line 13 deduction</t>
+  </si>
+  <si>
+    <t>job.filing_status is equal to "QSS"</t>
+  </si>
+  <si>
+    <t>Married Filing Separately</t>
+  </si>
+  <si>
+    <t>job.filing_status is equal to "MFS"</t>
+  </si>
+  <si>
+    <t>*</t>
   </si>
   <si>
     <t>ACTIONS: COMMENTS</t>
@@ -69,6 +88,51 @@
     <t>DSL: ACTIONS</t>
   </si>
   <si>
+    <t>Married Filing Jointly / Surviving Spouse / Head of Household column</t>
+  </si>
+  <si>
+    <t>set result.nm_limit_1 = nm_joint_bracket_1_limit; set result.nm_limit_2 = nm_joint_bracket_2_limit; set result.nm_limit_3 = nm_joint_bracket_3_limit; set result.nm_limit_4 = nm_joint_bracket_4_limit; set result.nm_high_base = nm_joint_high_base; set result.nm_top_threshold = nm_joint_bracket_5_limit; set result.nm_top_base = nm_joint_top_base; set result.nm_lmi_limit = nm_lmi_limit_joint; set result.nm_lmi_base = nm_lmi_base_joint; set result.nm_lmi_rate = nm_lmi_rate_joint</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>Married Filing Separately column</t>
+  </si>
+  <si>
+    <t>set result.nm_limit_1 = nm_mfs_bracket_1_limit; set result.nm_limit_2 = nm_mfs_bracket_2_limit; set result.nm_limit_3 = nm_mfs_bracket_3_limit; set result.nm_limit_4 = nm_mfs_bracket_4_limit; set result.nm_high_base = nm_mfs_high_base; set result.nm_top_threshold = nm_mfs_bracket_5_limit; set result.nm_top_base = nm_mfs_top_base; set result.nm_lmi_limit = nm_lmi_limit_mfs; set result.nm_lmi_base = nm_lmi_base_mfs; set result.nm_lmi_rate = nm_lmi_rate_mfs</t>
+  </si>
+  <si>
+    <t>Line 13: $4,000 per dependent after the first</t>
+  </si>
+  <si>
+    <t>set result.nm_dependent_deduction = (the maximum of (length of job.dependents - 1) and 0) * nm_dependent_deduction_amount</t>
+  </si>
+  <si>
+    <t>Line 12 federal standard deduction; line 14 low- and middle-income exemption worksheet, rounded to the dollar</t>
+  </si>
+  <si>
+    <t>set result.nm_std_deduction = result.standard_deduction; set result.nm_exemptions = length of job.taxpayers + length of job.dependents; if result.state_calc_agi &lt;= result.nm_lmi_limit then { set result.nm_lmi_exemption = the floor of ((the maximum of (nm_low_middle_income_exemption - result.nm_lmi_rate * (the maximum of (result.state_calc_agi - result.nm_lmi_base) and 0.0)) and 0.0) * result.nm_exemptions + 0.5); } else { set result.nm_lmi_exemption = 0.0; } endif</t>
+  </si>
+  <si>
+    <t>Line 17 taxable income; line 18 tax from the rate table</t>
+  </si>
+  <si>
+    <t>set result.nm_taxable_income = the maximum of (result.state_calc_agi - result.nm_std_deduction - result.nm_dependent_deduction - result.nm_lmi_exemption) and 0.0; perform NM_Tax_Table; set result.nm_tax = result.nm_table_tax</t>
+  </si>
+  <si>
+    <t>Harvested onto the roster by Compute_Roster_State_Tax</t>
+  </si>
+  <si>
+    <t>set result.computed_state_taxable_income = result.nm_taxable_income; set result.computed_state_tax = result.nm_tax</t>
+  </si>
+  <si>
+    <t>Audit</t>
+  </si>
+  <si>
+    <t>add "  New Mexico (PIT-1 2025): taxable income $" + result.nm_taxable_income + " (standard deduction $" + result.nm_std_deduction + ", dependents $" + result.nm_dependent_deduction + ", low/middle-income exemption $" + result.nm_lmi_exemption + "), tax $" + result.nm_tax to job.audit_trail</t>
+  </si>
+  <si>
     <t>DT: NM Military Retirement Exclusion</t>
   </si>
   <si>
@@ -78,6 +142,57 @@
     <t>TABLE_NUMBER: 43101</t>
   </si>
   <si>
+    <t>DT: NM Tax Table</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMMENTS: </t>
+  </si>
+  <si>
+    <t>TABLE_NUMBER: 43110</t>
+  </si>
+  <si>
+    <t>set result.nm_band_midpoint = (the ceiling of (result.nm_taxable_income / 100.0)) * 100.0 - 50.0</t>
+  </si>
+  <si>
+    <t>$60 or less</t>
+  </si>
+  <si>
+    <t>result.nm_taxable_income &lt;= nm_zero_limit</t>
+  </si>
+  <si>
+    <t>Through $100,000: the table</t>
+  </si>
+  <si>
+    <t>result.nm_taxable_income &lt;= nm_table_limit</t>
+  </si>
+  <si>
+    <t>Over $100,000, not over the 5.9% threshold</t>
+  </si>
+  <si>
+    <t>result.nm_taxable_income &lt;= result.nm_top_threshold</t>
+  </si>
+  <si>
+    <t>set result.nm_table_tax = 0.0</t>
+  </si>
+  <si>
+    <t>Bracket tax at the band midpoint, rounded</t>
+  </si>
+  <si>
+    <t>set result.nm_table_tax = the floor of (nm_bracket_1_rate * (the minimum of result.nm_band_midpoint and result.nm_limit_1) + nm_bracket_2_rate * (the maximum of ((the minimum of result.nm_band_midpoint and result.nm_limit_2) - result.nm_limit_1) and 0.0) + nm_bracket_3_rate * (the maximum of ((the minimum of result.nm_band_midpoint and result.nm_limit_3) - result.nm_limit_2) and 0.0) + nm_bracket_4_rate * (the maximum of ((the minimum of result.nm_band_midpoint and result.nm_limit_4) - result.nm_limit_3) and 0.0) + nm_bracket_5_rate * (the maximum of (result.nm_band_midpoint - result.nm_limit_4) and 0.0) + 0.5)</t>
+  </si>
+  <si>
+    <t>Page T-7: base + 4.9% over $100,000</t>
+  </si>
+  <si>
+    <t>set result.nm_table_tax = the floor of (result.nm_high_base + nm_bracket_5_rate * (result.nm_taxable_income - nm_table_limit) + 0.5)</t>
+  </si>
+  <si>
+    <t>Page T-7: base + 5.9% over the threshold</t>
+  </si>
+  <si>
+    <t>set result.nm_table_tax = the floor of (result.nm_top_base + nm_bracket_6_rate * (result.nm_taxable_income - result.nm_top_threshold) + 0.5)</t>
+  </si>
+  <si>
     <t>EDD: EDD</t>
   </si>
   <si>
@@ -123,15 +238,27 @@
     <t>result</t>
   </si>
   <si>
-    <t>(31 attributes)</t>
+    <t>(70 attributes)</t>
+  </si>
+  <si>
+    <t>nm_band_midpoint</t>
+  </si>
+  <si>
+    <t>double</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>rw</t>
+  </si>
+  <si>
+    <t>NM tax computation (nm_tax)</t>
   </si>
   <si>
     <t>nm_base_tax</t>
   </si>
   <si>
-    <t>double</t>
-  </si>
-  <si>
     <t>0.0</t>
   </si>
   <si>
@@ -195,49 +322,85 @@
     <t>NM tax rate bracket 6: 5.9% (2025). Top marginal rate.</t>
   </si>
   <si>
+    <t>nm_dependent_deduction</t>
+  </si>
+  <si>
+    <t>nm_dependent_deduction_amount</t>
+  </si>
+  <si>
+    <t>4000</t>
+  </si>
+  <si>
+    <t>PIT-1 line 13 worksheet: $4,000 per dependent after the first (HOH and MFJ only)</t>
+  </si>
+  <si>
+    <t>nm_exemptions</t>
+  </si>
+  <si>
+    <t>nm_high_base</t>
+  </si>
+  <si>
     <t>nm_joint_bracket_1_limit</t>
   </si>
   <si>
-    <t>8000.0</t>
-  </si>
-  <si>
-    <t>NM bracket 1 upper limit joint (2025). Source: NM TRD</t>
+    <t>8000</t>
+  </si>
+  <si>
+    <t>NM 2025 PIT-1 Tax Rate Table (PIT-TRT): MFJ/HOH/QSS 1.5% bracket top</t>
   </si>
   <si>
     <t>nm_joint_bracket_2_limit</t>
   </si>
   <si>
-    <t>24000.0</t>
-  </si>
-  <si>
-    <t>NM bracket 2 upper limit joint (2025)</t>
+    <t>25000</t>
+  </si>
+  <si>
+    <t>NM 2025 PIT-1 Tax Rate Table (PIT-TRT): MFJ/HOH/QSS 3.2% bracket top</t>
   </si>
   <si>
     <t>nm_joint_bracket_3_limit</t>
   </si>
   <si>
-    <t>48000.0</t>
-  </si>
-  <si>
-    <t>NM bracket 3 upper limit joint (2025)</t>
+    <t>50000</t>
+  </si>
+  <si>
+    <t>NM 2025 PIT-1 Tax Rate Table (PIT-TRT): MFJ/HOH/QSS 4.3% bracket top</t>
   </si>
   <si>
     <t>nm_joint_bracket_4_limit</t>
   </si>
   <si>
-    <t>96000.0</t>
-  </si>
-  <si>
-    <t>NM bracket 4 upper limit joint (2025)</t>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>NM 2025 PIT-1 Tax Rate Table (PIT-TRT): MFJ/HOH/QSS 4.7% bracket top</t>
   </si>
   <si>
     <t>nm_joint_bracket_5_limit</t>
   </si>
   <si>
-    <t>315000.0</t>
-  </si>
-  <si>
-    <t>NM bracket 5 upper limit joint (2025)</t>
+    <t>315000</t>
+  </si>
+  <si>
+    <t>NM 2025 PIT-1 Tax Rate Table (PIT-TRT): MFJ/HOH/QSS 4.9% bracket top</t>
+  </si>
+  <si>
+    <t>nm_joint_high_base</t>
+  </si>
+  <si>
+    <t>4087</t>
+  </si>
+  <si>
+    <t>NM 2025 PIT-1 Tax Rate Table (PIT-TRT) p.T-7: MFJ/HOH over $100,000, not over $315,000: $4,087 + 4.9% over $100,000</t>
+  </si>
+  <si>
+    <t>nm_joint_top_base</t>
+  </si>
+  <si>
+    <t>14622</t>
+  </si>
+  <si>
+    <t>NM 2025 PIT-1 Tax Rate Table (PIT-TRT) p.T-7: MFJ/HOH over $315,000: $14,622 + 5.9% over $315,000</t>
   </si>
   <si>
     <t>nm_lictr_income_limit</t>
@@ -282,13 +445,172 @@
     <t>NM LICTR rebate amount (computed)</t>
   </si>
   <si>
+    <t>nm_limit_1</t>
+  </si>
+  <si>
+    <t>nm_limit_2</t>
+  </si>
+  <si>
+    <t>nm_limit_3</t>
+  </si>
+  <si>
+    <t>nm_limit_4</t>
+  </si>
+  <si>
+    <t>nm_lmi_base</t>
+  </si>
+  <si>
+    <t>nm_lmi_base_joint</t>
+  </si>
+  <si>
+    <t>30000</t>
+  </si>
+  <si>
+    <t>PIT-1 line 14 worksheet line 2, MFJ, Surviving Spouse, HOH</t>
+  </si>
+  <si>
+    <t>nm_lmi_base_mfs</t>
+  </si>
+  <si>
+    <t>15000</t>
+  </si>
+  <si>
+    <t>PIT-1 line 14 worksheet line 2, MFS</t>
+  </si>
+  <si>
+    <t>nm_lmi_base_single</t>
+  </si>
+  <si>
+    <t>20000</t>
+  </si>
+  <si>
+    <t>PIT-1 line 14 worksheet line 2, Single</t>
+  </si>
+  <si>
+    <t>nm_lmi_exemption</t>
+  </si>
+  <si>
+    <t>nm_lmi_limit</t>
+  </si>
+  <si>
+    <t>nm_lmi_limit_joint</t>
+  </si>
+  <si>
+    <t>55000</t>
+  </si>
+  <si>
+    <t>PIT-1 line 14: MFJ, Surviving Spouse, HOH eligible with federal AGI $55,000 or less</t>
+  </si>
+  <si>
+    <t>nm_lmi_limit_mfs</t>
+  </si>
+  <si>
+    <t>27500</t>
+  </si>
+  <si>
+    <t>PIT-1 line 14: MFS eligible with federal AGI $27,500 or less</t>
+  </si>
+  <si>
+    <t>nm_lmi_limit_single</t>
+  </si>
+  <si>
+    <t>36667</t>
+  </si>
+  <si>
+    <t>PIT-1 line 14: Single eligible with federal AGI $36,667 or less</t>
+  </si>
+  <si>
+    <t>nm_lmi_rate</t>
+  </si>
+  <si>
+    <t>nm_lmi_rate_joint</t>
+  </si>
+  <si>
+    <t>0.10</t>
+  </si>
+  <si>
+    <t>PIT-1 line 14 worksheet line 4, MFJ, Surviving Spouse, HOH</t>
+  </si>
+  <si>
+    <t>nm_lmi_rate_mfs</t>
+  </si>
+  <si>
+    <t>0.20</t>
+  </si>
+  <si>
+    <t>PIT-1 line 14 worksheet line 4, MFS</t>
+  </si>
+  <si>
+    <t>nm_lmi_rate_single</t>
+  </si>
+  <si>
+    <t>0.15</t>
+  </si>
+  <si>
+    <t>PIT-1 line 14 worksheet line 4, Single</t>
+  </si>
+  <si>
     <t>nm_low_middle_income_exemption</t>
   </si>
   <si>
-    <t>2500.0</t>
-  </si>
-  <si>
-    <t>NM low and middle income exemption per qualified exemption (2025). Source: NM TRD</t>
+    <t>2500</t>
+  </si>
+  <si>
+    <t>PIT-1 line 14 worksheet: $2,500 per exemption before the reduction</t>
+  </si>
+  <si>
+    <t>nm_mfs_bracket_1_limit</t>
+  </si>
+  <si>
+    <t>NM 2025 PIT-1 Tax Rate Table (PIT-TRT): MFS 1.5% bracket top</t>
+  </si>
+  <si>
+    <t>nm_mfs_bracket_2_limit</t>
+  </si>
+  <si>
+    <t>12500</t>
+  </si>
+  <si>
+    <t>NM 2025 PIT-1 Tax Rate Table (PIT-TRT): MFS 3.2% bracket top</t>
+  </si>
+  <si>
+    <t>nm_mfs_bracket_3_limit</t>
+  </si>
+  <si>
+    <t>NM 2025 PIT-1 Tax Rate Table (PIT-TRT): MFS 4.3% bracket top</t>
+  </si>
+  <si>
+    <t>nm_mfs_bracket_4_limit</t>
+  </si>
+  <si>
+    <t>NM 2025 PIT-1 Tax Rate Table (PIT-TRT): MFS 4.7% bracket top</t>
+  </si>
+  <si>
+    <t>nm_mfs_bracket_5_limit</t>
+  </si>
+  <si>
+    <t>157500</t>
+  </si>
+  <si>
+    <t>NM 2025 PIT-1 Tax Rate Table (PIT-TRT): MFS 4.9% bracket top</t>
+  </si>
+  <si>
+    <t>nm_mfs_high_base</t>
+  </si>
+  <si>
+    <t>4492</t>
+  </si>
+  <si>
+    <t>NM 2025 PIT-1 Tax Rate Table (PIT-TRT) p.T-7: MFS over $100,000, not over $157,500: $4,492 + 4.9% over $100,000</t>
+  </si>
+  <si>
+    <t>nm_mfs_top_base</t>
+  </si>
+  <si>
+    <t>7310</t>
+  </si>
+  <si>
+    <t>NM 2025 PIT-1 Tax Rate Table (PIT-TRT) p.T-7: MFS over $157,500: $7,310 + 5.9% over $157,500</t>
   </si>
   <si>
     <t>nm_military_retirement_exemption</t>
@@ -351,6 +673,24 @@
     <t>NM bracket 5 upper limit single (2025)</t>
   </si>
   <si>
+    <t>nm_single_high_base</t>
+  </si>
+  <si>
+    <t>4356</t>
+  </si>
+  <si>
+    <t>NM 2025 PIT-1 Tax Rate Table (PIT-TRT) p.T-7: Single over $100,000, not over $210,000: $4,356 + 4.9% over $100,000</t>
+  </si>
+  <si>
+    <t>nm_single_top_base</t>
+  </si>
+  <si>
+    <t>9746</t>
+  </si>
+  <si>
+    <t>NM 2025 PIT-1 Tax Rate Table (PIT-TRT) p.T-7: Single over $210,000: $9,746 + 5.9% over $210,000</t>
+  </si>
+  <si>
     <t>nm_standard_deduction_hoh</t>
   </si>
   <si>
@@ -381,6 +721,18 @@
     <t>NM standard deduction single (2025). Source: NM TRD</t>
   </si>
   <si>
+    <t>nm_std_deduction</t>
+  </si>
+  <si>
+    <t>nm_table_limit</t>
+  </si>
+  <si>
+    <t>NM 2025 PIT-1 Tax Rate Table (PIT-TRT): the table covers taxable income through $100,000; over it, the schedule on page T-7</t>
+  </si>
+  <si>
+    <t>nm_table_tax</t>
+  </si>
+  <si>
     <t>nm_tax</t>
   </si>
   <si>
@@ -391,6 +743,21 @@
   </si>
   <si>
     <t>NM taxable income after deductions (computed)</t>
+  </si>
+  <si>
+    <t>nm_top_base</t>
+  </si>
+  <si>
+    <t>nm_top_threshold</t>
+  </si>
+  <si>
+    <t>nm_zero_limit</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>NM 2025 PIT-1 Tax Rate Table (PIT-TRT): taxable income not over $60 has no tax</t>
   </si>
 </sst>
 </file>
@@ -986,181 +1353,739 @@
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1" t="s">
+    <row r="9">
+      <c r="A9" s="5">
+        <v>1</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+      <c r="S9" s="3"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="1">
         <v>1</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E11" s="1">
         <v>2</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F11" s="1">
         <v>3</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G11" s="1">
         <v>4</v>
       </c>
-      <c r="H10" s="1">
+      <c r="H11" s="1">
         <v>5</v>
       </c>
-      <c r="I10" s="1">
+      <c r="I11" s="1">
         <v>6</v>
       </c>
-      <c r="J10" s="1">
+      <c r="J11" s="1">
         <v>7</v>
       </c>
-      <c r="K10" s="1">
-        <v>8</v>
-      </c>
-      <c r="L10" s="1">
+      <c r="K11" s="1">
+        <v>8</v>
+      </c>
+      <c r="L11" s="1">
         <v>9</v>
       </c>
-      <c r="M10" s="1">
+      <c r="M11" s="1">
         <v>10</v>
       </c>
-      <c r="N10" s="1">
+      <c r="N11" s="1">
         <v>11</v>
       </c>
-      <c r="O10" s="1">
+      <c r="O11" s="1">
         <v>12</v>
       </c>
-      <c r="P10" s="1">
+      <c r="P11" s="1">
         <v>13</v>
       </c>
-      <c r="Q10" s="1">
+      <c r="Q11" s="1">
         <v>14</v>
       </c>
-      <c r="R10" s="1">
+      <c r="R11" s="1">
         <v>15</v>
       </c>
-      <c r="S10" s="1">
+      <c r="S11" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="5">
+    <row r="12">
+      <c r="A12" s="5">
         <v>1</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5">
+        <v>2</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5">
+        <v>3</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="4">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4">
+        <v>2</v>
+      </c>
+      <c r="F16" s="4">
+        <v>3</v>
+      </c>
+      <c r="G16" s="4">
+        <v>4</v>
+      </c>
+      <c r="H16" s="4">
+        <v>5</v>
+      </c>
+      <c r="I16" s="4">
+        <v>6</v>
+      </c>
+      <c r="J16" s="4">
+        <v>7</v>
+      </c>
+      <c r="K16" s="4">
+        <v>8</v>
+      </c>
+      <c r="L16" s="4">
+        <v>9</v>
+      </c>
+      <c r="M16" s="4">
         <v>10</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="N16" s="4">
         <v>11</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="O16" s="4">
         <v>12</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="2" t="s">
+      <c r="P16" s="4">
         <v>13</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="Q16" s="4">
         <v>14</v>
       </c>
-      <c r="H11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="S11" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="s">
+      <c r="R16" s="4">
         <v>15</v>
       </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1" t="s">
+      <c r="S16" s="4">
         <v>16</v>
       </c>
-      <c r="D13" s="4">
+    </row>
+    <row r="17">
+      <c r="A17" s="5">
         <v>1</v>
       </c>
-      <c r="E13" s="4">
+      <c r="B17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5">
         <v>2</v>
       </c>
-      <c r="F13" s="4">
+      <c r="B18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5">
         <v>3</v>
       </c>
-      <c r="G13" s="4">
+      <c r="B19" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5">
         <v>4</v>
       </c>
-      <c r="H13" s="4">
+      <c r="B20" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5">
         <v>5</v>
       </c>
-      <c r="I13" s="4">
+      <c r="B21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5">
         <v>6</v>
       </c>
-      <c r="J13" s="4">
+      <c r="B22" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5">
         <v>7</v>
       </c>
-      <c r="K13" s="4">
-        <v>8</v>
-      </c>
-      <c r="L13" s="4">
-        <v>9</v>
-      </c>
-      <c r="M13" s="4">
-        <v>10</v>
-      </c>
-      <c r="N13" s="4">
-        <v>11</v>
-      </c>
-      <c r="O13" s="4">
-        <v>12</v>
-      </c>
-      <c r="P13" s="4">
-        <v>13</v>
-      </c>
-      <c r="Q13" s="4">
-        <v>14</v>
-      </c>
-      <c r="R13" s="4">
-        <v>15</v>
-      </c>
-      <c r="S13" s="4">
-        <v>16</v>
+      <c r="B23" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A3:S3"/>
@@ -1169,8 +2094,9 @@
     <mergeCell ref="C6:S6"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C8:S8"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C9:S9"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A16:B16"/>
   </mergeCells>
 </worksheet>
 </file>
@@ -1186,7 +2112,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1232,7 +2158,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -1255,7 +2181,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1328,11 +2254,11 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -1385,11 +2311,11 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D12" s="4">
         <v>1</v>
@@ -1460,6 +2386,728 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
+    <col customWidth="true" max="1" min="1" width="20"/>
+    <col customWidth="true" max="3" min="2" width="40"/>
+    <col customWidth="true" max="19" min="4" width="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5">
+        <v>1</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+      <c r="S9" s="3"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2</v>
+      </c>
+      <c r="F11" s="1">
+        <v>3</v>
+      </c>
+      <c r="G11" s="1">
+        <v>4</v>
+      </c>
+      <c r="H11" s="1">
+        <v>5</v>
+      </c>
+      <c r="I11" s="1">
+        <v>6</v>
+      </c>
+      <c r="J11" s="1">
+        <v>7</v>
+      </c>
+      <c r="K11" s="1">
+        <v>8</v>
+      </c>
+      <c r="L11" s="1">
+        <v>9</v>
+      </c>
+      <c r="M11" s="1">
+        <v>10</v>
+      </c>
+      <c r="N11" s="1">
+        <v>11</v>
+      </c>
+      <c r="O11" s="1">
+        <v>12</v>
+      </c>
+      <c r="P11" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>14</v>
+      </c>
+      <c r="R11" s="1">
+        <v>15</v>
+      </c>
+      <c r="S11" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5">
+        <v>1</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5">
+        <v>2</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5">
+        <v>3</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="4">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4">
+        <v>2</v>
+      </c>
+      <c r="F16" s="4">
+        <v>3</v>
+      </c>
+      <c r="G16" s="4">
+        <v>4</v>
+      </c>
+      <c r="H16" s="4">
+        <v>5</v>
+      </c>
+      <c r="I16" s="4">
+        <v>6</v>
+      </c>
+      <c r="J16" s="4">
+        <v>7</v>
+      </c>
+      <c r="K16" s="4">
+        <v>8</v>
+      </c>
+      <c r="L16" s="4">
+        <v>9</v>
+      </c>
+      <c r="M16" s="4">
+        <v>10</v>
+      </c>
+      <c r="N16" s="4">
+        <v>11</v>
+      </c>
+      <c r="O16" s="4">
+        <v>12</v>
+      </c>
+      <c r="P16" s="4">
+        <v>13</v>
+      </c>
+      <c r="Q16" s="4">
+        <v>14</v>
+      </c>
+      <c r="R16" s="4">
+        <v>15</v>
+      </c>
+      <c r="S16" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5">
+        <v>1</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5">
+        <v>2</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5">
+        <v>3</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5">
+        <v>4</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A3:S3"/>
+    <mergeCell ref="A4:S4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:S6"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:S8"/>
+    <mergeCell ref="C9:S9"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A16:B16"/>
+  </mergeCells>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
     <col customWidth="true" max="1" min="1" width="18"/>
     <col customWidth="true" max="2" min="2" width="25"/>
     <col customWidth="true" max="3" min="3" width="10"/>
@@ -1476,56 +3124,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>33</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -1541,1273 +3189,2872 @@
     </row>
     <row r="4">
       <c r="A4" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>47</v>
+        <v>86</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>59</v>
+        <v>98</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>61</v>
+        <v>100</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>66</v>
+        <v>103</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>67</v>
+        <v>104</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>68</v>
+        <v>105</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>71</v>
+        <v>106</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E18" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="F18" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>39</v>
-      </c>
       <c r="H18" s="16" t="s">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>84</v>
+        <v>117</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>86</v>
+        <v>119</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>87</v>
+        <v>121</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M20" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>89</v>
+        <v>123</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>91</v>
+        <v>125</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>93</v>
+        <v>127</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M22" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>94</v>
+        <v>128</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>38</v>
+        <v>129</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>96</v>
+        <v>131</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>97</v>
+        <v>132</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M24" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>99</v>
+        <v>134</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>100</v>
+        <v>135</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>101</v>
+        <v>136</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M25" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>102</v>
+        <v>137</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>103</v>
+        <v>138</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="H26" s="16" t="s">
-        <v>104</v>
+        <v>139</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M26" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>107</v>
+        <v>141</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L27" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M27" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>108</v>
+        <v>142</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="H28" s="16" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K28" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M28" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="H29" s="16" t="s">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J29" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L29" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M29" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>114</v>
+        <v>144</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>115</v>
+        <v>76</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="H30" s="16" t="s">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K30" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L30" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M30" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>117</v>
+        <v>145</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="H31" s="16" t="s">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J31" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L31" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M31" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="H32" s="16" t="s">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K32" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L32" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M32" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>38</v>
+        <v>148</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="H33" s="16" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J33" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K33" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L33" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M33" s="8" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>38</v>
+        <v>151</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="H34" s="16" t="s">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K34" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L34" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M34" s="7" t="s">
-        <v>14</v>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H35" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M35" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H36" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="I36" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J36" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K36" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L36" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M36" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="H37" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="I37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M37" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="H38" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="I38" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J38" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K38" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L38" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M38" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H39" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="I39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M39" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="H40" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="I40" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J40" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K40" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L40" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M40" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="H41" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="I41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M41" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G42" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="H42" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="I42" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J42" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K42" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L42" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M42" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H43" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="I43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M43" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="H44" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="I44" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K44" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L44" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M44" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H45" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="I45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G46" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="H46" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="I46" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J46" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K46" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L46" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M46" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H47" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="I47" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K47" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L47" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M47" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G48" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="H48" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="I48" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J48" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K48" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L48" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M48" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H49" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="I49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M49" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G50" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="H50" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="I50" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J50" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K50" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L50" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M50" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G51" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H51" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="I51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L51" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M51" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="H52" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="I52" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J52" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K52" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L52" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M52" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="C53" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H53" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="I53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M53" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B54" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G54" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="H54" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="I54" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J54" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K54" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L54" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M54" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B55" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="C55" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H55" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="I55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M55" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B56" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="C56" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G56" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="H56" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="I56" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J56" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K56" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L56" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M56" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B57" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="C57" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G57" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H57" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="I57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M57" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B58" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="C58" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G58" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="H58" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="I58" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J58" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K58" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L58" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M58" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B59" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G59" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H59" s="16" t="s">
+        <v>217</v>
+      </c>
+      <c r="I59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M59" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B60" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="C60" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="F60" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G60" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="H60" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="I60" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J60" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K60" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L60" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M60" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="C61" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G61" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H61" s="16" t="s">
+        <v>223</v>
+      </c>
+      <c r="I61" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J61" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K61" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L61" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M61" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B62" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="C62" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="F62" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G62" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="H62" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="I62" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K62" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L62" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M62" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B63" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="C63" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G63" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H63" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="I63" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J63" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K63" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L63" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M63" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B64" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="C64" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="F64" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G64" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="H64" s="16" t="s">
+        <v>231</v>
+      </c>
+      <c r="I64" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J64" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K64" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L64" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M64" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B65" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="C65" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G65" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H65" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="I65" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J65" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K65" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L65" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M65" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="C66" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="F66" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G66" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H66" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="I66" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J66" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K66" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L66" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M66" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B67" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="C67" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G67" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H67" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="I67" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J67" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K67" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L67" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M67" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B68" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="C68" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="F68" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G68" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H68" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="I68" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J68" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K68" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L68" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M68" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="C69" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G69" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H69" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="I69" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J69" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K69" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L69" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M69" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B70" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="C70" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E70" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="F70" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G70" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="H70" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="I70" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J70" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K70" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L70" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M70" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="C71" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E71" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G71" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="H71" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="I71" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J71" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K71" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L71" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M71" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B72" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="C72" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="F72" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G72" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H72" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="I72" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J72" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K72" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L72" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M72" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B73" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="C73" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G73" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H73" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="I73" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J73" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K73" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L73" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M73" s="8" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/sampleprojects/TaxReturn/excel/states/NM.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/NM.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="259">
   <si>
     <t>DT: nm tax</t>
   </si>
@@ -46,7 +46,7 @@
     <t/>
   </si>
   <si>
-    <t>set result.nm_limit_1 = nm_single_bracket_1_limit; set result.nm_limit_2 = nm_single_bracket_2_limit; set result.nm_limit_3 = nm_single_bracket_3_limit; set result.nm_limit_4 = nm_single_bracket_4_limit; set result.nm_high_base = nm_single_high_base; set result.nm_top_threshold = nm_single_bracket_5_limit; set result.nm_top_base = nm_single_top_base; set result.nm_lmi_limit = nm_lmi_limit_single; set result.nm_lmi_base = nm_lmi_base_single; set result.nm_lmi_rate = nm_lmi_rate_single; set result.nm_dependent_deduction = 0.0</t>
+    <t>set result.nm_limit_1 = nm_single_bracket_1_limit; set result.nm_limit_2 = nm_single_bracket_2_limit; set result.nm_limit_3 = nm_single_bracket_3_limit; set result.nm_limit_4 = nm_single_bracket_4_limit; set result.nm_high_base = nm_single_high_base; set result.nm_top_threshold = nm_single_bracket_5_limit; set result.nm_top_base = nm_single_top_base; set result.nm_lmi_limit = nm_lmi_limit_single; set result.nm_lmi_base = nm_lmi_base_single; set result.nm_lmi_rate = nm_lmi_rate_single; set result.nm_dependent_deduction = 0.0; set result.nm_military_retirement_exclusion = 0.0; perform NM_Military_Retirement_Exclusion</t>
   </si>
   <si>
     <t>CONDITIONS: COMMENTS</t>
@@ -115,10 +115,10 @@
     <t>set result.nm_std_deduction = result.standard_deduction; set result.nm_exemptions = length of job.taxpayers + length of job.dependents; if result.state_calc_agi &lt;= result.nm_lmi_limit then { set result.nm_lmi_exemption = the floor of ((the maximum of (nm_low_middle_income_exemption - result.nm_lmi_rate * (the maximum of (result.state_calc_agi - result.nm_lmi_base) and 0.0)) and 0.0) * result.nm_exemptions + 0.5); } else { set result.nm_lmi_exemption = 0.0; } endif</t>
   </si>
   <si>
-    <t>Line 17 taxable income; line 18 tax from the rate table</t>
-  </si>
-  <si>
-    <t>set result.nm_taxable_income = the maximum of (result.state_calc_agi - result.nm_std_deduction - result.nm_dependent_deduction - result.nm_lmi_exemption) and 0.0; perform NM_Tax_Table; set result.nm_tax = result.nm_table_tax</t>
+    <t>Line 15 PIT-ADJ exemptions (armed forces retirement pay, line 24); line 17 taxable income; line 18 tax from the rate table</t>
+  </si>
+  <si>
+    <t>set result.nm_taxable_income = the maximum of (result.state_calc_agi - result.nm_military_retirement_exclusion - result.nm_std_deduction - result.nm_dependent_deduction - result.nm_lmi_exemption) and 0.0; perform NM_Tax_Table; set result.nm_tax = result.nm_table_tax</t>
   </si>
   <si>
     <t>Harvested onto the roster by Compute_Roster_State_Tax</t>
@@ -130,7 +130,7 @@
     <t>Audit</t>
   </si>
   <si>
-    <t>add "  New Mexico (PIT-1 2025): taxable income $" + result.nm_taxable_income + " (standard deduction $" + result.nm_std_deduction + ", dependents $" + result.nm_dependent_deduction + ", low/middle-income exemption $" + result.nm_lmi_exemption + "), tax $" + result.nm_tax to job.audit_trail</t>
+    <t>add "  New Mexico (PIT-1 2025): taxable income $" + result.nm_taxable_income + " (armed forces retirement pay exemption $" + result.nm_military_retirement_exclusion + ", standard deduction $" + result.nm_std_deduction + ", dependents $" + result.nm_dependent_deduction + ", low/middle-income exemption $" + result.nm_lmi_exemption + "), tax $" + result.nm_tax to job.audit_trail</t>
   </si>
   <si>
     <t>DT: NM Military Retirement Exclusion</t>
@@ -142,6 +142,36 @@
     <t>TABLE_NUMBER: 43101</t>
   </si>
   <si>
+    <t>for all taxpayers</t>
+  </si>
+  <si>
+    <t>The taxpayer is an armed forces retiree with retirement pay in net income</t>
+  </si>
+  <si>
+    <t>taxpayer.military_retirement_pay &gt; 0</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Schedule PIT-ADJ line 24: $30,000 of armed forces retirement pay per qualifying retiree (Section 7-2-5.13 NMSA 1978)</t>
+  </si>
+  <si>
+    <t>add the minimum of taxpayer.military_retirement_pay and nm_military_retirement_exemption to result.nm_military_retirement_exclusion</t>
+  </si>
+  <si>
+    <t>Policy:</t>
+  </si>
+  <si>
+    <t>Policy Statements</t>
+  </si>
+  <si>
+    <t>Exemption for armed forces retirement pay, Schedule PIT-ADJ line 24 -&gt; PIT-1 line 15: the lesser of the pay and $30,000 per armed forces retiree or surviving spouse (Section 7-2-5.13 NMSA 1978 as amended by 2024 SB 56; 2025 PIT-ADJ instructions). No age or residency-date limit.</t>
+  </si>
+  <si>
+    <t>No armed forces retirement pay for this taxpayer.</t>
+  </si>
+  <si>
     <t>DT: NM Tax Table</t>
   </si>
   <si>
@@ -238,7 +268,7 @@
     <t>result</t>
   </si>
   <si>
-    <t>(70 attributes)</t>
+    <t>(71 attributes)</t>
   </si>
   <si>
     <t>nm_band_midpoint</t>
@@ -613,13 +643,19 @@
     <t>NM 2025 PIT-1 Tax Rate Table (PIT-TRT) p.T-7: MFS over $157,500: $7,310 + 5.9% over $157,500</t>
   </si>
   <si>
+    <t>nm_military_retirement_exclusion</t>
+  </si>
+  <si>
+    <t>New Mexico exemption for armed forces retirement pay (computed per taxpayer by NM_Military_Retirement_Exclusion): the lesser of the pay and $30,000 per armed forces retiree, Schedule PIT-ADJ line 24 -&gt; PIT-1 line 15 (Section 7-2-5.13 NMSA 1978 as amended by 2024 SB 56) (#1330).</t>
+  </si>
+  <si>
     <t>nm_military_retirement_exemption</t>
   </si>
   <si>
     <t>30000.0</t>
   </si>
   <si>
-    <t>NM military retirement exemption amount for 2025-2026 (2025). Source: MOAA State Report Card</t>
+    <t>NM exemption for armed forces retirement pay, $30,000 per qualifying retiree or surviving spouse for 2025 (Schedule PIT-ADJ line 24 and instructions; Section 7-2-5.13 NMSA 1978, $30,000 from 2024, sunset removed by 2024 SB 56). No age or residency-date limit.</t>
   </si>
   <si>
     <t>nm_military_retirement_taxable</t>
@@ -2227,157 +2263,479 @@
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="s">
+    <row r="7">
+      <c r="A7" s="5">
+        <v>1</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1" t="s">
+      <c r="B9" s="1"/>
+      <c r="C9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-      <c r="Q8" s="1"/>
-      <c r="R8" s="1"/>
-      <c r="S8" s="1"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="s">
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1" t="s">
+      <c r="B11" s="1"/>
+      <c r="C11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D11" s="1">
         <v>1</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E11" s="1">
         <v>2</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F11" s="1">
         <v>3</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G11" s="1">
         <v>4</v>
       </c>
-      <c r="H10" s="1">
+      <c r="H11" s="1">
         <v>5</v>
       </c>
-      <c r="I10" s="1">
+      <c r="I11" s="1">
         <v>6</v>
       </c>
-      <c r="J10" s="1">
+      <c r="J11" s="1">
         <v>7</v>
       </c>
-      <c r="K10" s="1">
-        <v>8</v>
-      </c>
-      <c r="L10" s="1">
+      <c r="K11" s="1">
+        <v>8</v>
+      </c>
+      <c r="L11" s="1">
         <v>9</v>
       </c>
-      <c r="M10" s="1">
+      <c r="M11" s="1">
         <v>10</v>
       </c>
-      <c r="N10" s="1">
+      <c r="N11" s="1">
         <v>11</v>
       </c>
-      <c r="O10" s="1">
+      <c r="O11" s="1">
         <v>12</v>
       </c>
-      <c r="P10" s="1">
+      <c r="P11" s="1">
         <v>13</v>
       </c>
-      <c r="Q10" s="1">
+      <c r="Q11" s="1">
         <v>14</v>
       </c>
-      <c r="R10" s="1">
+      <c r="R11" s="1">
         <v>15</v>
       </c>
-      <c r="S10" s="1">
+      <c r="S11" s="1">
         <v>16</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="5">
+        <v>1</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1" t="s">
+      <c r="B14" s="1"/>
+      <c r="C14" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D14" s="4">
         <v>1</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E14" s="4">
         <v>2</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F14" s="4">
         <v>3</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G14" s="4">
         <v>4</v>
       </c>
-      <c r="H12" s="4">
+      <c r="H14" s="4">
         <v>5</v>
       </c>
-      <c r="I12" s="4">
+      <c r="I14" s="4">
         <v>6</v>
       </c>
-      <c r="J12" s="4">
+      <c r="J14" s="4">
         <v>7</v>
       </c>
-      <c r="K12" s="4">
-        <v>8</v>
-      </c>
-      <c r="L12" s="4">
+      <c r="K14" s="4">
+        <v>8</v>
+      </c>
+      <c r="L14" s="4">
         <v>9</v>
       </c>
-      <c r="M12" s="4">
+      <c r="M14" s="4">
         <v>10</v>
       </c>
-      <c r="N12" s="4">
+      <c r="N14" s="4">
         <v>11</v>
       </c>
-      <c r="O12" s="4">
+      <c r="O14" s="4">
         <v>12</v>
       </c>
-      <c r="P12" s="4">
+      <c r="P14" s="4">
         <v>13</v>
       </c>
-      <c r="Q12" s="4">
+      <c r="Q14" s="4">
         <v>14</v>
       </c>
-      <c r="R12" s="4">
+      <c r="R14" s="4">
         <v>15</v>
       </c>
-      <c r="S12" s="4">
+      <c r="S14" s="4">
         <v>16</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="5">
+        <v>1</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
+      <c r="E17" s="1">
+        <v>2</v>
+      </c>
+      <c r="F17" s="1">
+        <v>3</v>
+      </c>
+      <c r="G17" s="1">
+        <v>4</v>
+      </c>
+      <c r="H17" s="1">
+        <v>5</v>
+      </c>
+      <c r="I17" s="1">
+        <v>6</v>
+      </c>
+      <c r="J17" s="1">
+        <v>7</v>
+      </c>
+      <c r="K17" s="1">
+        <v>8</v>
+      </c>
+      <c r="L17" s="1">
+        <v>9</v>
+      </c>
+      <c r="M17" s="1">
+        <v>10</v>
+      </c>
+      <c r="N17" s="1">
+        <v>11</v>
+      </c>
+      <c r="O17" s="1">
+        <v>12</v>
+      </c>
+      <c r="P17" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>14</v>
+      </c>
+      <c r="R17" s="1">
+        <v>15</v>
+      </c>
+      <c r="S17" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5">
+        <v>1</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5">
+        <v>2</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="12">
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A3:S3"/>
     <mergeCell ref="A4:S4"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C6:S6"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:S8"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C7:S7"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:S9"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A17:B17"/>
   </mergeCells>
 </worksheet>
 </file>
@@ -2393,7 +2751,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2439,7 +2797,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -2462,7 +2820,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -2541,7 +2899,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -2622,10 +2980,10 @@
         <v>1</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>14</v>
@@ -2681,10 +3039,10 @@
         <v>2</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>15</v>
@@ -2740,10 +3098,10 @@
         <v>3</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>15</v>
@@ -2859,7 +3217,7 @@
         <v>8</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>25</v>
@@ -2915,10 +3273,10 @@
         <v>2</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>8</v>
@@ -2974,10 +3332,10 @@
         <v>3</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>8</v>
@@ -3033,10 +3391,10 @@
         <v>4</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>8</v>
@@ -3124,56 +3482,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -3192,25 +3550,25 @@
         <v>8</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>8</v>
@@ -3233,25 +3591,25 @@
         <v>8</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>8</v>
@@ -3274,25 +3632,25 @@
         <v>8</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>8</v>
@@ -3315,25 +3673,25 @@
         <v>8</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>8</v>
@@ -3356,25 +3714,25 @@
         <v>8</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>8</v>
@@ -3397,25 +3755,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="I9" s="8" t="s">
         <v>8</v>
@@ -3438,25 +3796,25 @@
         <v>8</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>8</v>
@@ -3479,25 +3837,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="I11" s="8" t="s">
         <v>8</v>
@@ -3520,25 +3878,25 @@
         <v>8</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>8</v>
@@ -3561,25 +3919,25 @@
         <v>8</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I13" s="8" t="s">
         <v>8</v>
@@ -3602,25 +3960,25 @@
         <v>8</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>8</v>
@@ -3643,25 +4001,25 @@
         <v>8</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="I15" s="8" t="s">
         <v>8</v>
@@ -3684,25 +4042,25 @@
         <v>8</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>8</v>
@@ -3725,25 +4083,25 @@
         <v>8</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="I17" s="8" t="s">
         <v>8</v>
@@ -3766,25 +4124,25 @@
         <v>8</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="I18" s="7" t="s">
         <v>8</v>
@@ -3807,25 +4165,25 @@
         <v>8</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="I19" s="8" t="s">
         <v>8</v>
@@ -3848,25 +4206,25 @@
         <v>8</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="I20" s="7" t="s">
         <v>8</v>
@@ -3889,25 +4247,25 @@
         <v>8</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="I21" s="8" t="s">
         <v>8</v>
@@ -3930,25 +4288,25 @@
         <v>8</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="I22" s="7" t="s">
         <v>8</v>
@@ -3971,25 +4329,25 @@
         <v>8</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="I23" s="8" t="s">
         <v>8</v>
@@ -4012,25 +4370,25 @@
         <v>8</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="I24" s="7" t="s">
         <v>8</v>
@@ -4053,25 +4411,25 @@
         <v>8</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="I25" s="8" t="s">
         <v>8</v>
@@ -4094,25 +4452,25 @@
         <v>8</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H26" s="16" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="I26" s="7" t="s">
         <v>8</v>
@@ -4135,25 +4493,25 @@
         <v>8</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="I27" s="8" t="s">
         <v>8</v>
@@ -4176,25 +4534,25 @@
         <v>8</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H28" s="16" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="I28" s="7" t="s">
         <v>8</v>
@@ -4217,25 +4575,25 @@
         <v>8</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H29" s="16" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="I29" s="8" t="s">
         <v>8</v>
@@ -4258,25 +4616,25 @@
         <v>8</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D30" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="F30" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H30" s="16" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="I30" s="7" t="s">
         <v>8</v>
@@ -4299,25 +4657,25 @@
         <v>8</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H31" s="16" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="I31" s="8" t="s">
         <v>8</v>
@@ -4340,25 +4698,25 @@
         <v>8</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H32" s="16" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="I32" s="7" t="s">
         <v>8</v>
@@ -4381,25 +4739,25 @@
         <v>8</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D33" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H33" s="16" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="I33" s="8" t="s">
         <v>8</v>
@@ -4422,25 +4780,25 @@
         <v>8</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="F34" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H34" s="16" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="I34" s="7" t="s">
         <v>8</v>
@@ -4463,25 +4821,25 @@
         <v>8</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D35" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="F35" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H35" s="16" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="I35" s="8" t="s">
         <v>8</v>
@@ -4504,25 +4862,25 @@
         <v>8</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H36" s="16" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="I36" s="7" t="s">
         <v>8</v>
@@ -4545,25 +4903,25 @@
         <v>8</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D37" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H37" s="16" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="I37" s="8" t="s">
         <v>8</v>
@@ -4586,25 +4944,25 @@
         <v>8</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="F38" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H38" s="16" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="I38" s="7" t="s">
         <v>8</v>
@@ -4627,25 +4985,25 @@
         <v>8</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D39" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H39" s="16" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="I39" s="8" t="s">
         <v>8</v>
@@ -4668,25 +5026,25 @@
         <v>8</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D40" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="F40" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H40" s="16" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="I40" s="7" t="s">
         <v>8</v>
@@ -4709,25 +5067,25 @@
         <v>8</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D41" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H41" s="16" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="I41" s="8" t="s">
         <v>8</v>
@@ -4750,25 +5108,25 @@
         <v>8</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D42" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="F42" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H42" s="16" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="I42" s="7" t="s">
         <v>8</v>
@@ -4791,25 +5149,25 @@
         <v>8</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D43" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H43" s="16" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="I43" s="8" t="s">
         <v>8</v>
@@ -4832,25 +5190,25 @@
         <v>8</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D44" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="F44" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H44" s="16" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="I44" s="7" t="s">
         <v>8</v>
@@ -4873,25 +5231,25 @@
         <v>8</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D45" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H45" s="16" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="I45" s="8" t="s">
         <v>8</v>
@@ -4914,25 +5272,25 @@
         <v>8</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="F46" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H46" s="16" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="I46" s="7" t="s">
         <v>8</v>
@@ -4955,25 +5313,25 @@
         <v>8</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D47" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H47" s="16" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="I47" s="8" t="s">
         <v>8</v>
@@ -4996,25 +5354,25 @@
         <v>8</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D48" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="F48" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H48" s="16" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="I48" s="7" t="s">
         <v>8</v>
@@ -5037,25 +5395,25 @@
         <v>8</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D49" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H49" s="16" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="I49" s="8" t="s">
         <v>8</v>
@@ -5078,25 +5436,25 @@
         <v>8</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="F50" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H50" s="16" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="I50" s="7" t="s">
         <v>8</v>
@@ -5119,25 +5477,25 @@
         <v>8</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D51" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H51" s="16" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="I51" s="8" t="s">
         <v>8</v>
@@ -5160,25 +5518,25 @@
         <v>8</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D52" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="F52" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H52" s="16" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="I52" s="7" t="s">
         <v>8</v>
@@ -5201,25 +5559,25 @@
         <v>8</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D53" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>199</v>
+        <v>90</v>
       </c>
       <c r="F53" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="H53" s="16" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="I53" s="8" t="s">
         <v>8</v>
@@ -5242,25 +5600,25 @@
         <v>8</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D54" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>80</v>
+        <v>211</v>
       </c>
       <c r="F54" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H54" s="16" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="I54" s="7" t="s">
         <v>8</v>
@@ -5283,25 +5641,25 @@
         <v>8</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D55" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>204</v>
+        <v>90</v>
       </c>
       <c r="F55" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H55" s="16" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="I55" s="8" t="s">
         <v>8</v>
@@ -5324,25 +5682,25 @@
         <v>8</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D56" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="F56" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H56" s="16" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="I56" s="7" t="s">
         <v>8</v>
@@ -5365,25 +5723,25 @@
         <v>8</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D57" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="F57" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H57" s="16" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="I57" s="8" t="s">
         <v>8</v>
@@ -5406,25 +5764,25 @@
         <v>8</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D58" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="F58" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H58" s="16" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="I58" s="7" t="s">
         <v>8</v>
@@ -5447,25 +5805,25 @@
         <v>8</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D59" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="F59" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H59" s="16" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="I59" s="8" t="s">
         <v>8</v>
@@ -5488,25 +5846,25 @@
         <v>8</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D60" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="F60" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H60" s="16" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="I60" s="7" t="s">
         <v>8</v>
@@ -5529,25 +5887,25 @@
         <v>8</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D61" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="F61" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H61" s="16" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="I61" s="8" t="s">
         <v>8</v>
@@ -5570,25 +5928,25 @@
         <v>8</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D62" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="F62" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H62" s="16" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="I62" s="7" t="s">
         <v>8</v>
@@ -5611,25 +5969,25 @@
         <v>8</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D63" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="F63" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H63" s="16" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="I63" s="8" t="s">
         <v>8</v>
@@ -5652,25 +6010,25 @@
         <v>8</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D64" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="F64" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H64" s="16" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="I64" s="7" t="s">
         <v>8</v>
@@ -5693,25 +6051,25 @@
         <v>8</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D65" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F65" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H65" s="16" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="I65" s="8" t="s">
         <v>8</v>
@@ -5734,25 +6092,25 @@
         <v>8</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D66" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>76</v>
+        <v>237</v>
       </c>
       <c r="F66" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="H66" s="16" t="s">
-        <v>78</v>
+        <v>245</v>
       </c>
       <c r="I66" s="7" t="s">
         <v>8</v>
@@ -5775,25 +6133,25 @@
         <v>8</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D67" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="F67" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="H67" s="16" t="s">
-        <v>236</v>
+        <v>88</v>
       </c>
       <c r="I67" s="8" t="s">
         <v>8</v>
@@ -5816,25 +6174,25 @@
         <v>8</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D68" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="F68" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="H68" s="16" t="s">
-        <v>78</v>
+        <v>248</v>
       </c>
       <c r="I68" s="7" t="s">
         <v>8</v>
@@ -5857,25 +6215,25 @@
         <v>8</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D69" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F69" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="H69" s="16" t="s">
-        <v>239</v>
+        <v>88</v>
       </c>
       <c r="I69" s="8" t="s">
         <v>8</v>
@@ -5898,25 +6256,25 @@
         <v>8</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D70" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F70" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H70" s="16" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="I70" s="7" t="s">
         <v>8</v>
@@ -5939,25 +6297,25 @@
         <v>8</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D71" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="F71" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="H71" s="16" t="s">
-        <v>78</v>
+        <v>253</v>
       </c>
       <c r="I71" s="8" t="s">
         <v>8</v>
@@ -5980,25 +6338,25 @@
         <v>8</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D72" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="F72" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H72" s="16" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="I72" s="7" t="s">
         <v>8</v>
@@ -6021,25 +6379,25 @@
         <v>8</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D73" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>245</v>
+        <v>86</v>
       </c>
       <c r="F73" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="H73" s="16" t="s">
-        <v>246</v>
+        <v>88</v>
       </c>
       <c r="I73" s="8" t="s">
         <v>8</v>
@@ -6054,6 +6412,47 @@
         <v>8</v>
       </c>
       <c r="M73" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B74" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="C74" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E74" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="F74" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G74" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H74" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="I74" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J74" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K74" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L74" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M74" s="7" t="s">
         <v>8</v>
       </c>
     </row>

--- a/sampleprojects/TaxReturn/excel/states/NM.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/NM.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="262">
   <si>
     <t>DT: nm tax</t>
   </si>
@@ -154,6 +154,12 @@
     <t>N</t>
   </si>
   <si>
+    <t>Full-year resident entry only. A part-year or nonresident entry's income is built from the income entities, so the pension is not in it, and 4 U.S.C. 114 bars a state from taxing a nonresident's retirement income (#1330 review).</t>
+  </si>
+  <si>
+    <t>result.state_calc_resident_status is equal to "full_year"</t>
+  </si>
+  <si>
     <t>Schedule PIT-ADJ line 24: $30,000 of armed forces retirement pay per qualifying retiree (Section 7-2-5.13 NMSA 1978)</t>
   </si>
   <si>
@@ -170,6 +176,9 @@
   </si>
   <si>
     <t>No armed forces retirement pay for this taxpayer.</t>
+  </si>
+  <si>
+    <t>Not a full-year resident entry: the pension is not in this entry's sourced income (the roster builds it from the income entities) and 4 U.S.C. 114 bars taxing a nonresident's retirement income, so nothing is subtracted.</t>
   </si>
   <si>
     <t>DT: NM Tax Table</t>
@@ -2389,7 +2398,7 @@
         <v>44</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>8</v>
@@ -2431,294 +2440,412 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="s">
+    <row r="13">
+      <c r="A13" s="5">
+        <v>2</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1" t="s">
+      <c r="B15" s="1"/>
+      <c r="C15" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D15" s="4">
         <v>1</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E15" s="4">
         <v>2</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F15" s="4">
         <v>3</v>
       </c>
-      <c r="G14" s="4">
+      <c r="G15" s="4">
         <v>4</v>
       </c>
-      <c r="H14" s="4">
+      <c r="H15" s="4">
         <v>5</v>
       </c>
-      <c r="I14" s="4">
+      <c r="I15" s="4">
         <v>6</v>
       </c>
-      <c r="J14" s="4">
+      <c r="J15" s="4">
         <v>7</v>
       </c>
-      <c r="K14" s="4">
-        <v>8</v>
-      </c>
-      <c r="L14" s="4">
+      <c r="K15" s="4">
+        <v>8</v>
+      </c>
+      <c r="L15" s="4">
         <v>9</v>
       </c>
-      <c r="M14" s="4">
+      <c r="M15" s="4">
         <v>10</v>
       </c>
-      <c r="N14" s="4">
+      <c r="N15" s="4">
         <v>11</v>
       </c>
-      <c r="O14" s="4">
+      <c r="O15" s="4">
         <v>12</v>
       </c>
-      <c r="P14" s="4">
+      <c r="P15" s="4">
         <v>13</v>
       </c>
-      <c r="Q14" s="4">
+      <c r="Q15" s="4">
         <v>14</v>
       </c>
-      <c r="R14" s="4">
+      <c r="R15" s="4">
         <v>15</v>
       </c>
-      <c r="S14" s="4">
+      <c r="S15" s="4">
         <v>16</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5">
+    <row r="16">
+      <c r="A16" s="5">
         <v>1</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D15" s="2" t="s">
+      <c r="B16" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S15" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D17" s="1">
+      <c r="E16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="1">
         <v>1</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E18" s="1">
         <v>2</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F18" s="1">
         <v>3</v>
       </c>
-      <c r="G17" s="1">
+      <c r="G18" s="1">
         <v>4</v>
       </c>
-      <c r="H17" s="1">
+      <c r="H18" s="1">
         <v>5</v>
       </c>
-      <c r="I17" s="1">
+      <c r="I18" s="1">
         <v>6</v>
       </c>
-      <c r="J17" s="1">
+      <c r="J18" s="1">
         <v>7</v>
       </c>
-      <c r="K17" s="1">
-        <v>8</v>
-      </c>
-      <c r="L17" s="1">
+      <c r="K18" s="1">
+        <v>8</v>
+      </c>
+      <c r="L18" s="1">
         <v>9</v>
       </c>
-      <c r="M17" s="1">
+      <c r="M18" s="1">
         <v>10</v>
       </c>
-      <c r="N17" s="1">
+      <c r="N18" s="1">
         <v>11</v>
       </c>
-      <c r="O17" s="1">
+      <c r="O18" s="1">
         <v>12</v>
       </c>
-      <c r="P17" s="1">
+      <c r="P18" s="1">
         <v>13</v>
       </c>
-      <c r="Q17" s="1">
+      <c r="Q18" s="1">
         <v>14</v>
       </c>
-      <c r="R17" s="1">
+      <c r="R18" s="1">
         <v>15</v>
       </c>
-      <c r="S17" s="1">
+      <c r="S18" s="1">
         <v>16</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5">
-        <v>1</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S18" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5">
+        <v>1</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5">
         <v>2</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S19" s="2" t="s">
+      <c r="B20" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5">
+        <v>3</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S21" s="2" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2734,8 +2861,8 @@
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="C9:S9"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A18:B18"/>
   </mergeCells>
 </worksheet>
 </file>
@@ -2751,7 +2878,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2797,7 +2924,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -2820,7 +2947,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -2899,7 +3026,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -2980,10 +3107,10 @@
         <v>1</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>14</v>
@@ -3039,10 +3166,10 @@
         <v>2</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>15</v>
@@ -3098,10 +3225,10 @@
         <v>3</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>15</v>
@@ -3217,7 +3344,7 @@
         <v>8</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>25</v>
@@ -3273,10 +3400,10 @@
         <v>2</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>8</v>
@@ -3332,10 +3459,10 @@
         <v>3</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>8</v>
@@ -3391,10 +3518,10 @@
         <v>4</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>8</v>
@@ -3482,56 +3609,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -3550,25 +3677,25 @@
         <v>8</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>8</v>
@@ -3591,25 +3718,25 @@
         <v>8</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>8</v>
@@ -3632,25 +3759,25 @@
         <v>8</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>91</v>
-      </c>
       <c r="H6" s="16" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>8</v>
@@ -3673,25 +3800,25 @@
         <v>8</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>8</v>
@@ -3714,25 +3841,25 @@
         <v>8</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>8</v>
@@ -3755,25 +3882,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="I9" s="8" t="s">
         <v>8</v>
@@ -3796,25 +3923,25 @@
         <v>8</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>8</v>
@@ -3837,25 +3964,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="I11" s="8" t="s">
         <v>8</v>
@@ -3878,25 +4005,25 @@
         <v>8</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>8</v>
@@ -3919,25 +4046,25 @@
         <v>8</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="I13" s="8" t="s">
         <v>8</v>
@@ -3960,25 +4087,25 @@
         <v>8</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>8</v>
@@ -4001,25 +4128,25 @@
         <v>8</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I15" s="8" t="s">
         <v>8</v>
@@ -4042,25 +4169,25 @@
         <v>8</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>8</v>
@@ -4083,25 +4210,25 @@
         <v>8</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I17" s="8" t="s">
         <v>8</v>
@@ -4124,25 +4251,25 @@
         <v>8</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I18" s="7" t="s">
         <v>8</v>
@@ -4165,25 +4292,25 @@
         <v>8</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="I19" s="8" t="s">
         <v>8</v>
@@ -4206,25 +4333,25 @@
         <v>8</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="I20" s="7" t="s">
         <v>8</v>
@@ -4247,25 +4374,25 @@
         <v>8</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="I21" s="8" t="s">
         <v>8</v>
@@ -4288,25 +4415,25 @@
         <v>8</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="I22" s="7" t="s">
         <v>8</v>
@@ -4329,25 +4456,25 @@
         <v>8</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="I23" s="8" t="s">
         <v>8</v>
@@ -4370,25 +4497,25 @@
         <v>8</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="I24" s="7" t="s">
         <v>8</v>
@@ -4411,25 +4538,25 @@
         <v>8</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="I25" s="8" t="s">
         <v>8</v>
@@ -4452,25 +4579,25 @@
         <v>8</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H26" s="16" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="I26" s="7" t="s">
         <v>8</v>
@@ -4493,25 +4620,25 @@
         <v>8</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="I27" s="8" t="s">
         <v>8</v>
@@ -4534,25 +4661,25 @@
         <v>8</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H28" s="16" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I28" s="7" t="s">
         <v>8</v>
@@ -4575,25 +4702,25 @@
         <v>8</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H29" s="16" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I29" s="8" t="s">
         <v>8</v>
@@ -4616,25 +4743,25 @@
         <v>8</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D30" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F30" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H30" s="16" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I30" s="7" t="s">
         <v>8</v>
@@ -4657,25 +4784,25 @@
         <v>8</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H31" s="16" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I31" s="8" t="s">
         <v>8</v>
@@ -4698,25 +4825,25 @@
         <v>8</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H32" s="16" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I32" s="7" t="s">
         <v>8</v>
@@ -4739,25 +4866,25 @@
         <v>8</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D33" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H33" s="16" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="I33" s="8" t="s">
         <v>8</v>
@@ -4780,25 +4907,25 @@
         <v>8</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F34" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H34" s="16" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="I34" s="7" t="s">
         <v>8</v>
@@ -4821,25 +4948,25 @@
         <v>8</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D35" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F35" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H35" s="16" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="I35" s="8" t="s">
         <v>8</v>
@@ -4862,25 +4989,25 @@
         <v>8</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H36" s="16" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I36" s="7" t="s">
         <v>8</v>
@@ -4903,25 +5030,25 @@
         <v>8</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D37" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H37" s="16" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I37" s="8" t="s">
         <v>8</v>
@@ -4944,25 +5071,25 @@
         <v>8</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="F38" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H38" s="16" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="I38" s="7" t="s">
         <v>8</v>
@@ -4985,25 +5112,25 @@
         <v>8</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D39" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H39" s="16" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="I39" s="8" t="s">
         <v>8</v>
@@ -5026,25 +5153,25 @@
         <v>8</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D40" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F40" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H40" s="16" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="I40" s="7" t="s">
         <v>8</v>
@@ -5067,25 +5194,25 @@
         <v>8</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D41" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H41" s="16" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I41" s="8" t="s">
         <v>8</v>
@@ -5108,25 +5235,25 @@
         <v>8</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D42" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F42" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H42" s="16" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="I42" s="7" t="s">
         <v>8</v>
@@ -5149,25 +5276,25 @@
         <v>8</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D43" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H43" s="16" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="I43" s="8" t="s">
         <v>8</v>
@@ -5190,25 +5317,25 @@
         <v>8</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D44" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F44" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H44" s="16" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="I44" s="7" t="s">
         <v>8</v>
@@ -5231,25 +5358,25 @@
         <v>8</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D45" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H45" s="16" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="I45" s="8" t="s">
         <v>8</v>
@@ -5272,25 +5399,25 @@
         <v>8</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F46" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H46" s="16" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="I46" s="7" t="s">
         <v>8</v>
@@ -5313,25 +5440,25 @@
         <v>8</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D47" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H47" s="16" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="I47" s="8" t="s">
         <v>8</v>
@@ -5354,25 +5481,25 @@
         <v>8</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D48" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F48" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H48" s="16" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="I48" s="7" t="s">
         <v>8</v>
@@ -5395,25 +5522,25 @@
         <v>8</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D49" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H49" s="16" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="I49" s="8" t="s">
         <v>8</v>
@@ -5436,25 +5563,25 @@
         <v>8</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F50" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H50" s="16" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="I50" s="7" t="s">
         <v>8</v>
@@ -5477,25 +5604,25 @@
         <v>8</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D51" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H51" s="16" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="I51" s="8" t="s">
         <v>8</v>
@@ -5518,25 +5645,25 @@
         <v>8</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D52" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F52" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H52" s="16" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="I52" s="7" t="s">
         <v>8</v>
@@ -5559,25 +5686,25 @@
         <v>8</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D53" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E53" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G53" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="F53" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G53" s="8" t="s">
-        <v>87</v>
-      </c>
       <c r="H53" s="16" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="I53" s="8" t="s">
         <v>8</v>
@@ -5600,25 +5727,25 @@
         <v>8</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D54" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="F54" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H54" s="16" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="I54" s="7" t="s">
         <v>8</v>
@@ -5641,25 +5768,25 @@
         <v>8</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D55" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F55" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H55" s="16" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="I55" s="8" t="s">
         <v>8</v>
@@ -5682,25 +5809,25 @@
         <v>8</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D56" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F56" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H56" s="16" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="I56" s="7" t="s">
         <v>8</v>
@@ -5723,25 +5850,25 @@
         <v>8</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D57" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="F57" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H57" s="16" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="I57" s="8" t="s">
         <v>8</v>
@@ -5764,25 +5891,25 @@
         <v>8</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D58" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F58" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H58" s="16" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="I58" s="7" t="s">
         <v>8</v>
@@ -5805,25 +5932,25 @@
         <v>8</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D59" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F59" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H59" s="16" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="I59" s="8" t="s">
         <v>8</v>
@@ -5846,25 +5973,25 @@
         <v>8</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D60" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="F60" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H60" s="16" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="I60" s="7" t="s">
         <v>8</v>
@@ -5887,25 +6014,25 @@
         <v>8</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D61" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="F61" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H61" s="16" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="I61" s="8" t="s">
         <v>8</v>
@@ -5928,25 +6055,25 @@
         <v>8</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D62" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="F62" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H62" s="16" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="I62" s="7" t="s">
         <v>8</v>
@@ -5969,25 +6096,25 @@
         <v>8</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D63" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="F63" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H63" s="16" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="I63" s="8" t="s">
         <v>8</v>
@@ -6010,25 +6137,25 @@
         <v>8</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D64" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F64" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H64" s="16" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="I64" s="7" t="s">
         <v>8</v>
@@ -6051,25 +6178,25 @@
         <v>8</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D65" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="F65" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H65" s="16" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="I65" s="8" t="s">
         <v>8</v>
@@ -6092,25 +6219,25 @@
         <v>8</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D66" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="F66" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H66" s="16" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="I66" s="7" t="s">
         <v>8</v>
@@ -6133,25 +6260,25 @@
         <v>8</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D67" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F67" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H67" s="16" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I67" s="8" t="s">
         <v>8</v>
@@ -6174,25 +6301,25 @@
         <v>8</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D68" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F68" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H68" s="16" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="I68" s="7" t="s">
         <v>8</v>
@@ -6215,25 +6342,25 @@
         <v>8</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D69" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F69" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H69" s="16" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I69" s="8" t="s">
         <v>8</v>
@@ -6256,25 +6383,25 @@
         <v>8</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D70" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F70" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H70" s="16" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="I70" s="7" t="s">
         <v>8</v>
@@ -6297,25 +6424,25 @@
         <v>8</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D71" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F71" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H71" s="16" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="I71" s="8" t="s">
         <v>8</v>
@@ -6338,25 +6465,25 @@
         <v>8</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D72" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F72" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H72" s="16" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I72" s="7" t="s">
         <v>8</v>
@@ -6379,25 +6506,25 @@
         <v>8</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D73" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F73" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H73" s="16" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I73" s="8" t="s">
         <v>8</v>
@@ -6420,25 +6547,25 @@
         <v>8</v>
       </c>
       <c r="B74" s="9" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D74" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="F74" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H74" s="16" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="I74" s="7" t="s">
         <v>8</v>

--- a/sampleprojects/TaxReturn/excel/states/NM.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/NM.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="262">
   <si>
     <t>DT: nm tax</t>
   </si>
@@ -46,7 +46,7 @@
     <t/>
   </si>
   <si>
-    <t>set result.nm_limit_1 = nm_single_bracket_1_limit; set result.nm_limit_2 = nm_single_bracket_2_limit; set result.nm_limit_3 = nm_single_bracket_3_limit; set result.nm_limit_4 = nm_single_bracket_4_limit; set result.nm_high_base = nm_single_high_base; set result.nm_top_threshold = nm_single_bracket_5_limit; set result.nm_top_base = nm_single_top_base; set result.nm_lmi_limit = nm_lmi_limit_single; set result.nm_lmi_base = nm_lmi_base_single; set result.nm_lmi_rate = nm_lmi_rate_single; set result.nm_dependent_deduction = 0.0</t>
+    <t>set result.nm_limit_1 = nm_single_bracket_1_limit; set result.nm_limit_2 = nm_single_bracket_2_limit; set result.nm_limit_3 = nm_single_bracket_3_limit; set result.nm_limit_4 = nm_single_bracket_4_limit; set result.nm_high_base = nm_single_high_base; set result.nm_top_threshold = nm_single_bracket_5_limit; set result.nm_top_base = nm_single_top_base; set result.nm_lmi_limit = nm_lmi_limit_single; set result.nm_lmi_base = nm_lmi_base_single; set result.nm_lmi_rate = nm_lmi_rate_single; set result.nm_dependent_deduction = 0.0; set result.nm_military_retirement_exclusion = 0.0; perform NM_Military_Retirement_Exclusion</t>
   </si>
   <si>
     <t>CONDITIONS: COMMENTS</t>
@@ -115,10 +115,10 @@
     <t>set result.nm_std_deduction = result.standard_deduction; set result.nm_exemptions = length of job.taxpayers + length of job.dependents; if result.state_calc_agi &lt;= result.nm_lmi_limit then { set result.nm_lmi_exemption = the floor of ((the maximum of (nm_low_middle_income_exemption - result.nm_lmi_rate * (the maximum of (result.state_calc_agi - result.nm_lmi_base) and 0.0)) and 0.0) * result.nm_exemptions + 0.5); } else { set result.nm_lmi_exemption = 0.0; } endif</t>
   </si>
   <si>
-    <t>Line 17 taxable income; line 18 tax from the rate table</t>
-  </si>
-  <si>
-    <t>set result.nm_taxable_income = the maximum of (result.state_calc_agi - result.nm_std_deduction - result.nm_dependent_deduction - result.nm_lmi_exemption) and 0.0; perform NM_Tax_Table; set result.nm_tax = result.nm_table_tax</t>
+    <t>Line 15 PIT-ADJ exemptions (armed forces retirement pay, line 24); line 17 taxable income; line 18 tax from the rate table</t>
+  </si>
+  <si>
+    <t>set result.nm_taxable_income = the maximum of (result.state_calc_agi - result.nm_military_retirement_exclusion - result.nm_std_deduction - result.nm_dependent_deduction - result.nm_lmi_exemption) and 0.0; perform NM_Tax_Table; set result.nm_tax = result.nm_table_tax</t>
   </si>
   <si>
     <t>Harvested onto the roster by Compute_Roster_State_Tax</t>
@@ -130,7 +130,7 @@
     <t>Audit</t>
   </si>
   <si>
-    <t>add "  New Mexico (PIT-1 2025): taxable income $" + result.nm_taxable_income + " (standard deduction $" + result.nm_std_deduction + ", dependents $" + result.nm_dependent_deduction + ", low/middle-income exemption $" + result.nm_lmi_exemption + "), tax $" + result.nm_tax to job.audit_trail</t>
+    <t>add "  New Mexico (PIT-1 2025): taxable income $" + result.nm_taxable_income + " (armed forces retirement pay exemption $" + result.nm_military_retirement_exclusion + ", standard deduction $" + result.nm_std_deduction + ", dependents $" + result.nm_dependent_deduction + ", low/middle-income exemption $" + result.nm_lmi_exemption + "), tax $" + result.nm_tax to job.audit_trail</t>
   </si>
   <si>
     <t>DT: NM Military Retirement Exclusion</t>
@@ -142,6 +142,45 @@
     <t>TABLE_NUMBER: 43101</t>
   </si>
   <si>
+    <t>for all taxpayers</t>
+  </si>
+  <si>
+    <t>The taxpayer is an armed forces retiree with retirement pay in net income</t>
+  </si>
+  <si>
+    <t>taxpayer.military_retirement_pay &gt; 0</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Full-year resident entry only. A part-year or nonresident entry's income is built from the income entities, so the pension is not in it, and 4 U.S.C. 114 bars a state from taxing a nonresident's retirement income (#1330 review).</t>
+  </si>
+  <si>
+    <t>result.state_calc_resident_status is equal to "full_year"</t>
+  </si>
+  <si>
+    <t>Schedule PIT-ADJ line 24: $30,000 of armed forces retirement pay per qualifying retiree (Section 7-2-5.13 NMSA 1978)</t>
+  </si>
+  <si>
+    <t>add the minimum of taxpayer.military_retirement_pay and nm_military_retirement_exemption to result.nm_military_retirement_exclusion</t>
+  </si>
+  <si>
+    <t>Policy:</t>
+  </si>
+  <si>
+    <t>Policy Statements</t>
+  </si>
+  <si>
+    <t>Exemption for armed forces retirement pay, Schedule PIT-ADJ line 24 -&gt; PIT-1 line 15: the lesser of the pay and $30,000 per armed forces retiree or surviving spouse (Section 7-2-5.13 NMSA 1978 as amended by 2024 SB 56; 2025 PIT-ADJ instructions). No age or residency-date limit.</t>
+  </si>
+  <si>
+    <t>No armed forces retirement pay for this taxpayer.</t>
+  </si>
+  <si>
+    <t>Not a full-year resident entry: the pension is not in this entry's sourced income (the roster builds it from the income entities) and 4 U.S.C. 114 bars taxing a nonresident's retirement income, so nothing is subtracted.</t>
+  </si>
+  <si>
     <t>DT: NM Tax Table</t>
   </si>
   <si>
@@ -238,7 +277,7 @@
     <t>result</t>
   </si>
   <si>
-    <t>(70 attributes)</t>
+    <t>(71 attributes)</t>
   </si>
   <si>
     <t>nm_band_midpoint</t>
@@ -613,13 +652,19 @@
     <t>NM 2025 PIT-1 Tax Rate Table (PIT-TRT) p.T-7: MFS over $157,500: $7,310 + 5.9% over $157,500</t>
   </si>
   <si>
+    <t>nm_military_retirement_exclusion</t>
+  </si>
+  <si>
+    <t>New Mexico exemption for armed forces retirement pay (computed per taxpayer by NM_Military_Retirement_Exclusion): the lesser of the pay and $30,000 per armed forces retiree, Schedule PIT-ADJ line 24 -&gt; PIT-1 line 15 (Section 7-2-5.13 NMSA 1978 as amended by 2024 SB 56) (#1330).</t>
+  </si>
+  <si>
     <t>nm_military_retirement_exemption</t>
   </si>
   <si>
     <t>30000.0</t>
   </si>
   <si>
-    <t>NM military retirement exemption amount for 2025-2026 (2025). Source: MOAA State Report Card</t>
+    <t>NM exemption for armed forces retirement pay, $30,000 per qualifying retiree or surviving spouse for 2025 (Schedule PIT-ADJ line 24 and instructions; Section 7-2-5.13 NMSA 1978, $30,000 from 2024, sunset removed by 2024 SB 56). No age or residency-date limit.</t>
   </si>
   <si>
     <t>nm_military_retirement_taxable</t>
@@ -2227,157 +2272,597 @@
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="s">
+    <row r="7">
+      <c r="A7" s="5">
+        <v>1</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1" t="s">
+      <c r="B9" s="1"/>
+      <c r="C9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-      <c r="Q8" s="1"/>
-      <c r="R8" s="1"/>
-      <c r="S8" s="1"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="s">
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1" t="s">
+      <c r="B11" s="1"/>
+      <c r="C11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D11" s="1">
         <v>1</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E11" s="1">
         <v>2</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F11" s="1">
         <v>3</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G11" s="1">
         <v>4</v>
       </c>
-      <c r="H10" s="1">
+      <c r="H11" s="1">
         <v>5</v>
       </c>
-      <c r="I10" s="1">
+      <c r="I11" s="1">
         <v>6</v>
       </c>
-      <c r="J10" s="1">
+      <c r="J11" s="1">
         <v>7</v>
       </c>
-      <c r="K10" s="1">
-        <v>8</v>
-      </c>
-      <c r="L10" s="1">
+      <c r="K11" s="1">
+        <v>8</v>
+      </c>
+      <c r="L11" s="1">
         <v>9</v>
       </c>
-      <c r="M10" s="1">
+      <c r="M11" s="1">
         <v>10</v>
       </c>
-      <c r="N10" s="1">
+      <c r="N11" s="1">
         <v>11</v>
       </c>
-      <c r="O10" s="1">
+      <c r="O11" s="1">
         <v>12</v>
       </c>
-      <c r="P10" s="1">
+      <c r="P11" s="1">
         <v>13</v>
       </c>
-      <c r="Q10" s="1">
+      <c r="Q11" s="1">
         <v>14</v>
       </c>
-      <c r="R10" s="1">
+      <c r="R11" s="1">
         <v>15</v>
       </c>
-      <c r="S10" s="1">
+      <c r="S11" s="1">
         <v>16</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="5">
+        <v>1</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5">
+        <v>2</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1" t="s">
+      <c r="B15" s="1"/>
+      <c r="C15" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D15" s="4">
         <v>1</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E15" s="4">
         <v>2</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F15" s="4">
         <v>3</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G15" s="4">
         <v>4</v>
       </c>
-      <c r="H12" s="4">
+      <c r="H15" s="4">
         <v>5</v>
       </c>
-      <c r="I12" s="4">
+      <c r="I15" s="4">
         <v>6</v>
       </c>
-      <c r="J12" s="4">
+      <c r="J15" s="4">
         <v>7</v>
       </c>
-      <c r="K12" s="4">
-        <v>8</v>
-      </c>
-      <c r="L12" s="4">
+      <c r="K15" s="4">
+        <v>8</v>
+      </c>
+      <c r="L15" s="4">
         <v>9</v>
       </c>
-      <c r="M12" s="4">
+      <c r="M15" s="4">
         <v>10</v>
       </c>
-      <c r="N12" s="4">
+      <c r="N15" s="4">
         <v>11</v>
       </c>
-      <c r="O12" s="4">
+      <c r="O15" s="4">
         <v>12</v>
       </c>
-      <c r="P12" s="4">
+      <c r="P15" s="4">
         <v>13</v>
       </c>
-      <c r="Q12" s="4">
+      <c r="Q15" s="4">
         <v>14</v>
       </c>
-      <c r="R12" s="4">
+      <c r="R15" s="4">
         <v>15</v>
       </c>
-      <c r="S12" s="4">
+      <c r="S15" s="4">
         <v>16</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="5">
+        <v>1</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1">
+        <v>2</v>
+      </c>
+      <c r="F18" s="1">
+        <v>3</v>
+      </c>
+      <c r="G18" s="1">
+        <v>4</v>
+      </c>
+      <c r="H18" s="1">
+        <v>5</v>
+      </c>
+      <c r="I18" s="1">
+        <v>6</v>
+      </c>
+      <c r="J18" s="1">
+        <v>7</v>
+      </c>
+      <c r="K18" s="1">
+        <v>8</v>
+      </c>
+      <c r="L18" s="1">
+        <v>9</v>
+      </c>
+      <c r="M18" s="1">
+        <v>10</v>
+      </c>
+      <c r="N18" s="1">
+        <v>11</v>
+      </c>
+      <c r="O18" s="1">
+        <v>12</v>
+      </c>
+      <c r="P18" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>14</v>
+      </c>
+      <c r="R18" s="1">
+        <v>15</v>
+      </c>
+      <c r="S18" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5">
+        <v>1</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5">
+        <v>2</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5">
+        <v>3</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="12">
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A3:S3"/>
     <mergeCell ref="A4:S4"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C6:S6"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:S8"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C7:S7"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:S9"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A18:B18"/>
   </mergeCells>
 </worksheet>
 </file>
@@ -2393,7 +2878,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2439,7 +2924,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -2462,7 +2947,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -2541,7 +3026,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -2622,10 +3107,10 @@
         <v>1</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>14</v>
@@ -2681,10 +3166,10 @@
         <v>2</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>15</v>
@@ -2740,10 +3225,10 @@
         <v>3</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>15</v>
@@ -2859,7 +3344,7 @@
         <v>8</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>25</v>
@@ -2915,10 +3400,10 @@
         <v>2</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>8</v>
@@ -2974,10 +3459,10 @@
         <v>3</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>8</v>
@@ -3033,10 +3518,10 @@
         <v>4</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>8</v>
@@ -3124,56 +3609,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -3192,25 +3677,25 @@
         <v>8</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>8</v>
@@ -3233,25 +3718,25 @@
         <v>8</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>8</v>
@@ -3274,25 +3759,25 @@
         <v>8</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>8</v>
@@ -3315,25 +3800,25 @@
         <v>8</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>8</v>
@@ -3356,25 +3841,25 @@
         <v>8</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>8</v>
@@ -3397,25 +3882,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="I9" s="8" t="s">
         <v>8</v>
@@ -3438,25 +3923,25 @@
         <v>8</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>8</v>
@@ -3479,25 +3964,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="I11" s="8" t="s">
         <v>8</v>
@@ -3520,25 +4005,25 @@
         <v>8</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>8</v>
@@ -3561,25 +4046,25 @@
         <v>8</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="I13" s="8" t="s">
         <v>8</v>
@@ -3602,25 +4087,25 @@
         <v>8</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>8</v>
@@ -3643,25 +4128,25 @@
         <v>8</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I15" s="8" t="s">
         <v>8</v>
@@ -3684,25 +4169,25 @@
         <v>8</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>8</v>
@@ -3725,25 +4210,25 @@
         <v>8</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="I17" s="8" t="s">
         <v>8</v>
@@ -3766,25 +4251,25 @@
         <v>8</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="I18" s="7" t="s">
         <v>8</v>
@@ -3807,25 +4292,25 @@
         <v>8</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="I19" s="8" t="s">
         <v>8</v>
@@ -3848,25 +4333,25 @@
         <v>8</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="I20" s="7" t="s">
         <v>8</v>
@@ -3889,25 +4374,25 @@
         <v>8</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="I21" s="8" t="s">
         <v>8</v>
@@ -3930,25 +4415,25 @@
         <v>8</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="I22" s="7" t="s">
         <v>8</v>
@@ -3971,25 +4456,25 @@
         <v>8</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="I23" s="8" t="s">
         <v>8</v>
@@ -4012,25 +4497,25 @@
         <v>8</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="I24" s="7" t="s">
         <v>8</v>
@@ -4053,25 +4538,25 @@
         <v>8</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="I25" s="8" t="s">
         <v>8</v>
@@ -4094,25 +4579,25 @@
         <v>8</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H26" s="16" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="I26" s="7" t="s">
         <v>8</v>
@@ -4135,25 +4620,25 @@
         <v>8</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="I27" s="8" t="s">
         <v>8</v>
@@ -4176,25 +4661,25 @@
         <v>8</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="H28" s="16" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I28" s="7" t="s">
         <v>8</v>
@@ -4217,25 +4702,25 @@
         <v>8</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="H29" s="16" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I29" s="8" t="s">
         <v>8</v>
@@ -4258,25 +4743,25 @@
         <v>8</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D30" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="F30" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="H30" s="16" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I30" s="7" t="s">
         <v>8</v>
@@ -4299,25 +4784,25 @@
         <v>8</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="H31" s="16" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I31" s="8" t="s">
         <v>8</v>
@@ -4340,25 +4825,25 @@
         <v>8</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="H32" s="16" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I32" s="7" t="s">
         <v>8</v>
@@ -4381,25 +4866,25 @@
         <v>8</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D33" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H33" s="16" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="I33" s="8" t="s">
         <v>8</v>
@@ -4422,25 +4907,25 @@
         <v>8</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="F34" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H34" s="16" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="I34" s="7" t="s">
         <v>8</v>
@@ -4463,25 +4948,25 @@
         <v>8</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D35" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="F35" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H35" s="16" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="I35" s="8" t="s">
         <v>8</v>
@@ -4504,25 +4989,25 @@
         <v>8</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="H36" s="16" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I36" s="7" t="s">
         <v>8</v>
@@ -4545,25 +5030,25 @@
         <v>8</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D37" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="H37" s="16" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I37" s="8" t="s">
         <v>8</v>
@@ -4586,25 +5071,25 @@
         <v>8</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="F38" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H38" s="16" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="I38" s="7" t="s">
         <v>8</v>
@@ -4627,25 +5112,25 @@
         <v>8</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D39" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H39" s="16" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="I39" s="8" t="s">
         <v>8</v>
@@ -4668,25 +5153,25 @@
         <v>8</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D40" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="F40" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H40" s="16" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="I40" s="7" t="s">
         <v>8</v>
@@ -4709,25 +5194,25 @@
         <v>8</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D41" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="H41" s="16" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I41" s="8" t="s">
         <v>8</v>
@@ -4750,25 +5235,25 @@
         <v>8</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D42" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="F42" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H42" s="16" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="I42" s="7" t="s">
         <v>8</v>
@@ -4791,25 +5276,25 @@
         <v>8</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D43" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H43" s="16" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="I43" s="8" t="s">
         <v>8</v>
@@ -4832,25 +5317,25 @@
         <v>8</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D44" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="F44" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H44" s="16" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="I44" s="7" t="s">
         <v>8</v>
@@ -4873,25 +5358,25 @@
         <v>8</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D45" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H45" s="16" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="I45" s="8" t="s">
         <v>8</v>
@@ -4914,25 +5399,25 @@
         <v>8</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="F46" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H46" s="16" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="I46" s="7" t="s">
         <v>8</v>
@@ -4955,25 +5440,25 @@
         <v>8</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D47" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H47" s="16" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="I47" s="8" t="s">
         <v>8</v>
@@ -4996,25 +5481,25 @@
         <v>8</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D48" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="F48" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H48" s="16" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="I48" s="7" t="s">
         <v>8</v>
@@ -5037,25 +5522,25 @@
         <v>8</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D49" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H49" s="16" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="I49" s="8" t="s">
         <v>8</v>
@@ -5078,25 +5563,25 @@
         <v>8</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="F50" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H50" s="16" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="I50" s="7" t="s">
         <v>8</v>
@@ -5119,25 +5604,25 @@
         <v>8</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D51" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H51" s="16" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="I51" s="8" t="s">
         <v>8</v>
@@ -5160,25 +5645,25 @@
         <v>8</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D52" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="F52" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H52" s="16" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="I52" s="7" t="s">
         <v>8</v>
@@ -5201,25 +5686,25 @@
         <v>8</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D53" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>199</v>
+        <v>93</v>
       </c>
       <c r="F53" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H53" s="16" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="I53" s="8" t="s">
         <v>8</v>
@@ -5242,25 +5727,25 @@
         <v>8</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D54" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>80</v>
+        <v>214</v>
       </c>
       <c r="F54" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H54" s="16" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="I54" s="7" t="s">
         <v>8</v>
@@ -5283,25 +5768,25 @@
         <v>8</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D55" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="F55" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H55" s="16" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="I55" s="8" t="s">
         <v>8</v>
@@ -5324,25 +5809,25 @@
         <v>8</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D56" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="F56" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H56" s="16" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="I56" s="7" t="s">
         <v>8</v>
@@ -5365,25 +5850,25 @@
         <v>8</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D57" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="F57" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H57" s="16" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="I57" s="8" t="s">
         <v>8</v>
@@ -5406,25 +5891,25 @@
         <v>8</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D58" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="F58" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H58" s="16" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="I58" s="7" t="s">
         <v>8</v>
@@ -5447,25 +5932,25 @@
         <v>8</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D59" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="F59" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H59" s="16" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="I59" s="8" t="s">
         <v>8</v>
@@ -5488,25 +5973,25 @@
         <v>8</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D60" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="F60" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H60" s="16" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="I60" s="7" t="s">
         <v>8</v>
@@ -5529,25 +6014,25 @@
         <v>8</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D61" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="F61" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H61" s="16" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="I61" s="8" t="s">
         <v>8</v>
@@ -5570,25 +6055,25 @@
         <v>8</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D62" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F62" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H62" s="16" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="I62" s="7" t="s">
         <v>8</v>
@@ -5611,25 +6096,25 @@
         <v>8</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D63" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="F63" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H63" s="16" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="I63" s="8" t="s">
         <v>8</v>
@@ -5652,25 +6137,25 @@
         <v>8</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D64" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="F64" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H64" s="16" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="I64" s="7" t="s">
         <v>8</v>
@@ -5693,25 +6178,25 @@
         <v>8</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D65" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="F65" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H65" s="16" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="I65" s="8" t="s">
         <v>8</v>
@@ -5734,25 +6219,25 @@
         <v>8</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D66" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>76</v>
+        <v>240</v>
       </c>
       <c r="F66" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="H66" s="16" t="s">
-        <v>78</v>
+        <v>248</v>
       </c>
       <c r="I66" s="7" t="s">
         <v>8</v>
@@ -5775,25 +6260,25 @@
         <v>8</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D67" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="F67" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H67" s="16" t="s">
-        <v>236</v>
+        <v>91</v>
       </c>
       <c r="I67" s="8" t="s">
         <v>8</v>
@@ -5816,25 +6301,25 @@
         <v>8</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D68" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c r="F68" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="H68" s="16" t="s">
-        <v>78</v>
+        <v>251</v>
       </c>
       <c r="I68" s="7" t="s">
         <v>8</v>
@@ -5857,25 +6342,25 @@
         <v>8</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D69" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="F69" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H69" s="16" t="s">
-        <v>239</v>
+        <v>91</v>
       </c>
       <c r="I69" s="8" t="s">
         <v>8</v>
@@ -5898,25 +6383,25 @@
         <v>8</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D70" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="F70" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H70" s="16" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="I70" s="7" t="s">
         <v>8</v>
@@ -5939,25 +6424,25 @@
         <v>8</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D71" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="F71" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="H71" s="16" t="s">
-        <v>78</v>
+        <v>256</v>
       </c>
       <c r="I71" s="8" t="s">
         <v>8</v>
@@ -5980,25 +6465,25 @@
         <v>8</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D72" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="F72" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="H72" s="16" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I72" s="7" t="s">
         <v>8</v>
@@ -6021,25 +6506,25 @@
         <v>8</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D73" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>245</v>
+        <v>89</v>
       </c>
       <c r="F73" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H73" s="16" t="s">
-        <v>246</v>
+        <v>91</v>
       </c>
       <c r="I73" s="8" t="s">
         <v>8</v>
@@ -6054,6 +6539,47 @@
         <v>8</v>
       </c>
       <c r="M73" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B74" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="C74" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E74" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="F74" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G74" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="H74" s="16" t="s">
+        <v>261</v>
+      </c>
+      <c r="I74" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J74" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K74" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L74" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M74" s="7" t="s">
         <v>8</v>
       </c>
     </row>
